--- a/LectioShed7.8/app_data/template_filieres.xlsx
+++ b/LectioShed7.8/app_data/template_filieres.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrani/Documents/codage/Valides/Testing/LectioShed7.5/app_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrani/Documents/codage/Valides/Testing/LectioShed7.8/app_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A460DF2E-1A56-B741-BC90-71B79151231E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C897EBE-A718-CB4F-B91E-987FFAA5062B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -187,9 +187,6 @@
     <t>S6DBD</t>
   </si>
   <si>
-    <t>Département Informatique</t>
-  </si>
-  <si>
     <t>Département de Biologie</t>
   </si>
   <si>
@@ -200,6 +197,9 @@
   </si>
   <si>
     <t>Département de Chimie</t>
+  </si>
+  <si>
+    <t>Département d'Informatique</t>
   </si>
 </sst>
 </file>
@@ -579,7 +579,7 @@
   <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="3" max="3" width="46.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -682,7 +682,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
@@ -691,26 +691,26 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
@@ -724,7 +724,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
@@ -752,7 +752,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
@@ -775,12 +775,12 @@
         <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
@@ -808,7 +808,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -817,12 +817,12 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
@@ -831,37 +831,34 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
         <v>5</v>
@@ -872,7 +869,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
@@ -883,51 +880,51 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
@@ -938,35 +935,35 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -977,117 +974,117 @@
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
         <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
         <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41" t="s">
         <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -1098,101 +1095,104 @@
         <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45" t="s">
         <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
         <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
         <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>55</v>
+        <v>6</v>
+      </c>
+      <c r="D50" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:D1 A3:D3 A2:C2 A5:D5 A4:C4 A8:D8 A6:C6 A7:C7 A14:D19 A9:C9 B10:C10 B11:C11 B12:C12 B13:C13" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:D1 A3:D3 A2:C2 A5:D5 A4:C4 A6:C6 A7:C7 A13:D18 A8:C8 B9:C9 B10:C10 B11:C11 B12:C12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>